--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -702,12 +702,16 @@
           <t>NSE:UNIONBANK26SEP190CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:27:06</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -730,8 +734,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>5.72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,125 @@
       <c r="AK2" t="n">
         <v>5.72</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:46:08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:SUZLON26SEP46PE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -829,12 +829,16 @@
           <t>NSE:SUZLON26SEP46PE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:47:45</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -857,8 +861,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,11 +834,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:47:45</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,7 +834,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:55:38</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -861,7 +865,7 @@
         <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,11 +834,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:55:38</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,7 +834,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:13:00</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -861,7 +865,7 @@
         <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,11 +834,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:13:00</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,7 +834,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:20:54</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -858,7 +862,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
         <v>1.15</v>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,11 +834,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:20:54</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,7 +834,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:24:04</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,11 +834,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:24:04</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -866,6 +862,117 @@
       </c>
       <c r="AK3" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:27:14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>72</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6400</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="S4" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:INOXWIND26SEP72.5PE</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,7 +834,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -974,6 +973,125 @@
           <t>2026-09-29</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:30:28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H5" t="n">
+        <v>87</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9275</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="S5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>31</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:IDFCFIRSTB26SEP87CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,6 +834,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:35:15</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -860,7 +865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="4">
@@ -1062,12 +1067,6 @@
           <t>NSE:IDFCFIRSTB26SEP87CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1090,8 +1089,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -956,6 +956,16 @@
           <t>NSE:INOXWIND26SEP72.5PE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:36:50</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -977,6 +987,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.65</v>
       </c>
     </row>
     <row r="5">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1083,6 +1083,16 @@
           <t>NSE:IDFCFIRSTB26SEP87CE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:39:59</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1104,6 +1114,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,11 +1088,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:39:59</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,7 +1088,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:44:47</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1115,7 +1119,7 @@
         <v>2.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,11 +1088,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:44:47</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,7 +1088,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:47:59</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1112,10 +1116,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,11 +1088,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:47:59</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1088,7 +1088,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:52:43</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1112,7 +1116,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="AK5" t="n">
         <v>2.06</v>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1083,9 +1083,14 @@
           <t>NSE:IDFCFIRSTB26SEP87CE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:57:49</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -956,9 +956,14 @@
           <t>NSE:INOXWIND26SEP72.5PE</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:00:25</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -992,7 +997,7 @@
         <v>3.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="5">
@@ -1091,11 +1096,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>Target 1 Hit</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 11:52:43</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,6 +1098,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:05:04</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1121,7 +1126,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="AK5" t="n">
         <v>2.06</v>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,11 +1098,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:05:04</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,7 +1098,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1127,6 +1126,125 @@
       <c r="AK5" t="n">
         <v>2.06</v>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:46:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>869.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="H6" t="n">
+        <v>870</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="K6" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="N6" t="n">
+        <v>500</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:GODREJCP26SEP870PE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1098,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13:39</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="6">
@@ -1215,12 +1220,6 @@
           <t>NSE:GODREJCP26SEP870PE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1243,8 +1242,117 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13:39</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>798.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H7" t="n">
+        <v>800</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1225</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>49</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26SEP800CE</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,11 +1098,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:13:39</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,7 +1098,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1327,6 +1326,16 @@
           <t>NSE:SONACOMS26SEP800CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:16:50</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1348,6 +1357,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22.4</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,6 +1098,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:19:58</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1329,11 +1334,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>Expired (no SL/Target hit)</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:16:50</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,11 +1098,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:19:58</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,7 +1098,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:23:07</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1359,6 +1363,117 @@
       </c>
       <c r="AK7" t="n">
         <v>22.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:23:07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>489.45</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>490</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K8" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>63.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:OIL26SEP490CE</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1098,11 +1098,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:23:07</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1453,6 +1448,16 @@
           <t>NSE:OIL26SEP490CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:24:42</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1474,6 +1479,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14.1</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1453,11 +1453,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:24:42</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1453,7 +1453,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:27:52</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1477,7 +1481,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="AK8" t="n">
         <v>14.1</v>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1453,11 +1453,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:27:52</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1093,9 +1093,14 @@
           <t>2026-09-03 11:57:49</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:33:03</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1453,7 +1458,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:34:10</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1481,10 +1486,121 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
         <v>14.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:34:10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5372</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I9" t="n">
+        <v>142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="K9" t="n">
+        <v>190.39</v>
+      </c>
+      <c r="L9" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>258.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>175</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:KEI26SEP5400CE</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1580,6 +1580,16 @@
           <t>NSE:KEI26SEP5400CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:37:22</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1601,6 +1611,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>142</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>137.85</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1585,11 +1585,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:37:22</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1585,7 +1585,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:40:33</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1612,7 +1616,7 @@
         <v>142</v>
       </c>
       <c r="AK9" t="n">
-        <v>137.85</v>
+        <v>135.6</v>
       </c>
     </row>
   </sheetData>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1458,11 +1458,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:34:10</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1458,7 +1458,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:46:53</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1485,7 +1489,7 @@
         <v>14.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="9">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1458,11 +1458,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 13:46:53</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1220,6 +1220,16 @@
           <t>NSE:GODREJCP26SEP870PE</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:10:33</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1241,6 +1251,12 @@
         <is>
           <t>2026-09-29</t>
         </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>14.85</v>
       </c>
     </row>
     <row r="7">
@@ -1458,7 +1474,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1103,6 +1103,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:12:49</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1126,10 +1131,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6">
@@ -1230,6 +1235,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:12:49</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1352,6 +1362,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:12:49</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1378,7 +1393,7 @@
         <v>23.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="8">
@@ -1474,6 +1489,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:12:48</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1497,10 +1517,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="9">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1235,11 +1235,7 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:12:49</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1235,7 +1235,11 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:14:41</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1103,11 +1103,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:12:49</t>
-        </is>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1235,11 +1230,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:14:41</t>
-        </is>
-      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1362,11 +1352,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:12:49</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1352,7 +1352,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1475,11 +1474,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:12:48</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1352,6 +1352,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:22:38</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1375,7 +1380,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>23.1</v>
+        <v>24.8</v>
       </c>
       <c r="AK7" t="n">
         <v>23.1</v>
@@ -1474,7 +1479,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1352,11 +1352,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:22:38</t>
-        </is>
-      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1479,6 +1474,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:24:12</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.2</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="9">

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1474,11 +1474,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:24:12</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1352,6 +1352,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:39:59</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1375,7 +1380,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>24.8</v>
+        <v>25.05</v>
       </c>
       <c r="AK7" t="n">
         <v>23.1</v>
@@ -1474,7 +1479,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:39:59</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1352,11 +1352,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:39:59</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -702,9 +702,14 @@
           <t>NSE:UNIONBANK26SEP190CE</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-09-03 15:16:10</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -735,10 +740,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>6.03</v>
+        <v>5.96</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.72</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="3">
@@ -1352,7 +1357,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1639,6 +1639,125 @@
       <c r="AK9" t="n">
         <v>135.6</v>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-03 15:30:12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1269</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="K10" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="L10" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="M10" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="N10" t="n">
+        <v>550</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:UNOMINDA26SEP1260CE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>v1 (2026-09-02)</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -1728,12 +1728,11 @@
           <t>NSE:UNOMINDA26SEP1260CE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed up ~31.65 (+1.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1756,8 +1755,6 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/signals_2026-09-03.xlsx
@@ -834,9 +834,24 @@
           <t>NSE:SUZLON26SEP46PE</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:43:00</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:09:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:21:00</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1352,9 +1367,14 @@
           <t>NSE:SONACOMS26SEP800CE</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:16:00</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1474,9 +1494,14 @@
           <t>NSE:OIL26SEP490CE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:22:00</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1601,9 +1626,14 @@
           <t>NSE:KEI26SEP5400CE</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:17:00</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1728,9 +1758,14 @@
           <t>NSE:UNOMINDA26SEP1260CE</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:15:00</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Closed up ~31.65 (+1.1% from entry, EOD estimate)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
